--- a/ruoyi-modules/ruoyi-vehicle/src/main/resources/assets/COC导入模版.xlsx
+++ b/ruoyi-modules/ruoyi-vehicle/src/main/resources/assets/COC导入模版.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="423">
   <si>
     <t>COC Template No.</t>
   </si>
@@ -860,9 +860,6 @@
   </si>
   <si>
     <t>235/50R19 103V 19x7J ET47 6.28N/kN C1</t>
-  </si>
-  <si>
-    <t>235/50 R19 103V 19x7J ET47 6.28N/kN C1</t>
   </si>
   <si>
     <t>Trailer brake connections mechanical</t>
@@ -3768,22 +3765,22 @@
         <v>269</v>
       </c>
       <c r="CZ3" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="DA3" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="DA3" s="1" t="s">
+      <c r="DB3" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="DB3" s="1" t="s">
+      <c r="DC3" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="DC3" s="1" t="s">
+      <c r="DD3" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="DD3" s="1" t="s">
+      <c r="DE3" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="DE3" s="1" t="s">
-        <v>275</v>
       </c>
       <c r="DF3" s="1" t="s">
         <v>226</v>
@@ -3793,19 +3790,19 @@
       </c>
       <c r="DH3" s="10"/>
       <c r="DI3" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="DJ3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="DJ3" s="1" t="s">
+      <c r="DK3" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="DK3" s="1" t="s">
+      <c r="DL3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="DM3" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="DL3" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="DM3" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="DN3" s="1" t="s">
         <v>226</v>
@@ -3815,19 +3812,19 @@
       </c>
       <c r="DP3" s="1"/>
       <c r="DQ3" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="DR3" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="DR3" s="1" t="s">
+      <c r="DS3" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="DS3" s="1" t="s">
+      <c r="DT3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="DU3" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="DT3" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="DU3" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="DV3" s="1" t="s">
         <v>226</v>
@@ -3839,97 +3836,97 @@
         <v>226</v>
       </c>
       <c r="DY3" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="DZ3" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="DZ3" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="EA3" s="1">
         <v>166.43</v>
       </c>
       <c r="EB3" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="EC3" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="EC3" s="1" t="s">
+      <c r="ED3" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="ED3" s="1" t="s">
+      <c r="EE3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EF3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EG3" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="EE3" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="EF3" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="EG3" s="1" t="s">
+      <c r="EH3" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="EH3" s="1" t="s">
+      <c r="EI3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EK3" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="EI3" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="EK3" s="1" t="s">
+      <c r="EL3" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="EL3" s="1" t="s">
+      <c r="EM3" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="EN3" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="EO3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EQ3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="ER3" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="EM3" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="EN3" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="EO3" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="EQ3" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="ER3" s="1" t="s">
+      <c r="ES3" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="ES3" s="1" t="s">
+      <c r="ET3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EU3" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="ET3" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="EU3" s="1" t="s">
+      <c r="EV3" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="EV3" s="1" t="s">
+      <c r="EW3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EX3" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="EW3" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="EX3" s="1" t="s">
+      <c r="EY3" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="EY3" s="1" t="s">
+      <c r="EZ3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="FA3" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="EZ3" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="FA3" s="1" t="s">
+      <c r="FB3" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="FB3" s="1" t="s">
+      <c r="FC3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="FD3" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="FC3" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="FD3" s="1" t="s">
+      <c r="FE3" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="FE3" s="1" t="s">
-        <v>302</v>
       </c>
       <c r="FF3" s="1" t="s">
         <v>226</v>
@@ -3953,94 +3950,94 @@
         <v>226</v>
       </c>
       <c r="FO3" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="FP3" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="FP3" s="1" t="s">
+      <c r="FQ3" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="FQ3" s="11" t="s">
+      <c r="FR3" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="FR3" s="1" t="s">
+      <c r="FS3" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="FS3" s="1" t="s">
+      <c r="FT3" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="FT3" s="11" t="s">
+      <c r="FU3" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="FU3" s="1" t="s">
+      <c r="FV3" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="FV3" s="1" t="s">
+      <c r="FW3" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="FW3" s="11" t="s">
+      <c r="FX3" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="FX3" s="1" t="s">
+      <c r="FY3" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="FY3" s="1" t="s">
+      <c r="FZ3" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="FZ3" s="11" t="s">
+      <c r="GC3" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="GC3" s="11" t="s">
+      <c r="GD3" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="GD3" s="1" t="s">
+      <c r="GE3" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="GE3" s="1" t="s">
+      <c r="GF3" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="GF3" s="11" t="s">
+      <c r="GG3" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="GG3" s="11" t="s">
+      <c r="GH3" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="GH3" s="11" t="s">
+      <c r="GI3" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="GI3" s="11" t="s">
+      <c r="GJ3" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="GJ3" s="11" t="s">
+      <c r="GK3" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="GK3" s="11" t="s">
+      <c r="GL3" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="GL3" s="1" t="s">
+      <c r="GM3" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="GM3" s="1" t="s">
+      <c r="GN3" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="GN3" s="1" t="s">
+      <c r="GO3" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="GP3" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="GO3" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="GP3" s="1" t="s">
+      <c r="GQ3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="GR3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="GS3" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="GQ3" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="GR3" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="GS3" s="1" t="s">
+      <c r="GT3" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="GT3" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="GU3" s="1" t="s">
         <v>214</v>
@@ -4051,19 +4048,19 @@
     </row>
     <row r="4" s="1" customFormat="1" ht="41" customHeight="1" spans="1:204">
       <c r="A4" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>334</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>210</v>
@@ -4075,7 +4072,7 @@
         <v>212</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>256</v>
@@ -4096,41 +4093,41 @@
         <v>216</v>
       </c>
       <c r="P4" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q4" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="Q4" s="7" t="s">
+      <c r="R4" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="U4" s="1"/>
       <c r="V4" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="W4" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="AB4" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>345</v>
       </c>
       <c r="AC4" s="1" t="s">
         <v>228</v>
@@ -4151,76 +4148,76 @@
         <v>232</v>
       </c>
       <c r="AI4" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="AJ4" s="1" t="s">
+      <c r="AK4" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="AK4" s="1" t="s">
-        <v>348</v>
       </c>
       <c r="AL4" s="1" t="s">
         <v>236</v>
       </c>
       <c r="AM4" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="AN4" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="AN4" s="1" t="s">
-        <v>350</v>
       </c>
       <c r="AO4" s="1" t="s">
         <v>239</v>
       </c>
       <c r="AP4" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AQ4" s="1" t="s">
         <v>241</v>
       </c>
       <c r="AR4" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AS4" s="7"/>
       <c r="AT4" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="AU4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="AV4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="AW4" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="AU4" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="AV4" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="AW4" s="1" t="s">
+      <c r="AX4" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="AX4" s="1" t="s">
+      <c r="AY4" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="AY4" s="1" t="s">
+      <c r="AZ4" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="AZ4" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="BA4" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="BB4" s="1"/>
       <c r="BC4" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BD4" s="1"/>
       <c r="BE4" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="BF4" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="BF4" s="1" t="s">
+      <c r="BG4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH4" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="BG4" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="BH4" s="1" t="s">
-        <v>360</v>
       </c>
       <c r="BI4" s="1"/>
       <c r="BJ4" s="1" t="s">
@@ -4236,25 +4233,25 @@
         <v>252</v>
       </c>
       <c r="BN4" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="BO4" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="BO4" s="7" t="s">
+      <c r="BP4" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="BP4" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="BQ4" s="1" t="s">
         <v>214</v>
       </c>
       <c r="BR4" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="BS4" s="1" t="s">
         <v>257</v>
       </c>
       <c r="BT4" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="BU4" s="1" t="s">
         <v>259</v>
@@ -4269,13 +4266,13 @@
         <v>261</v>
       </c>
       <c r="BY4" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="BZ4" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="BZ4" s="7" t="s">
+      <c r="CA4" s="7" t="s">
         <v>367</v>
-      </c>
-      <c r="CA4" s="7" t="s">
-        <v>368</v>
       </c>
       <c r="CB4" s="1" t="s">
         <v>263</v>
@@ -4316,38 +4313,38 @@
         <v>226</v>
       </c>
       <c r="CT4" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="CU4" s="7"/>
       <c r="CV4" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="CW4" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="CX4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CY4" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="CW4" s="1" t="s">
+      <c r="CZ4" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="CX4" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="CY4" s="1" t="s">
+      <c r="DA4" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="CZ4" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="DA4" s="1" t="s">
+      <c r="DB4" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="DB4" s="1" t="s">
+      <c r="DC4" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="DC4" s="1" t="s">
+      <c r="DD4" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="DE4" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="DD4" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="DE4" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="DF4" s="1" t="s">
         <v>226</v>
@@ -4357,41 +4354,41 @@
       </c>
       <c r="DH4" s="10"/>
       <c r="DI4" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="DJ4" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="DJ4" s="1" t="s">
+      <c r="DK4" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="DL4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="DM4" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="DK4" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="DL4" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="DM4" s="1" t="s">
+      <c r="DN4" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="DN4" s="1" t="s">
-        <v>379</v>
       </c>
       <c r="DO4" s="1" t="s">
         <v>226</v>
       </c>
       <c r="DP4" s="1"/>
       <c r="DQ4" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="DR4" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="DR4" s="1" t="s">
+      <c r="DS4" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="DS4" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="DT4" s="1" t="s">
         <v>226</v>
       </c>
       <c r="DU4" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="DV4" s="1" t="s">
         <v>226</v>
@@ -4403,100 +4400,100 @@
         <v>226</v>
       </c>
       <c r="DY4" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="DZ4" s="1" t="s">
         <v>226</v>
       </c>
       <c r="EA4" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="EB4" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="EB4" s="1" t="s">
+      <c r="EC4" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="EC4" s="1" t="s">
+      <c r="ED4" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="ED4" s="1" t="s">
+      <c r="EE4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EF4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EG4" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="EE4" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="EF4" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="EG4" s="1" t="s">
+      <c r="EH4" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="EH4" s="1" t="s">
+      <c r="EI4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EK4" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="EL4" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="EM4" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="EN4" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="EO4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EQ4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="ER4" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="EI4" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="EK4" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="EL4" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="EM4" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="EN4" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="EO4" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="EQ4" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="ER4" s="1" t="s">
+      <c r="ES4" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="ES4" s="1" t="s">
+      <c r="ET4" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="ET4" s="1" t="s">
+      <c r="EU4" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="EU4" s="1" t="s">
+      <c r="EV4" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="EW4" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="EV4" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="EW4" s="1" t="s">
+      <c r="EX4" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="EX4" s="1" t="s">
+      <c r="EY4" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="EY4" s="1" t="s">
+      <c r="EZ4" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="EZ4" s="1" t="s">
+      <c r="FA4" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="FB4" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="FA4" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="FB4" s="1" t="s">
+      <c r="FC4" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="FC4" s="1" t="s">
+      <c r="FD4" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="FD4" s="1" t="s">
+      <c r="FE4" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="FF4" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="FE4" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="FF4" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="FH4" s="1" t="s">
         <v>226</v>
@@ -4517,83 +4514,83 @@
         <v>226</v>
       </c>
       <c r="FO4" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="FP4" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="FP4" s="1" t="s">
+      <c r="FQ4" s="11" t="s">
         <v>402</v>
       </c>
-      <c r="FQ4" s="11" t="s">
+      <c r="FR4" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="FR4" s="1" t="s">
+      <c r="FS4" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="FS4" s="1" t="s">
+      <c r="FT4" s="11" t="s">
         <v>405</v>
       </c>
-      <c r="FT4" s="11" t="s">
+      <c r="FU4" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="FU4" s="1" t="s">
+      <c r="FV4" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="FV4" s="1" t="s">
+      <c r="FW4" s="11" t="s">
         <v>408</v>
       </c>
-      <c r="FW4" s="11" t="s">
+      <c r="FX4" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="FY4" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="FX4" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="FY4" s="1" t="s">
+      <c r="FZ4" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="GC4" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="FZ4" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="GC4" s="11" t="s">
+      <c r="GD4" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="GE4" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="GD4" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="GE4" s="1" t="s">
+      <c r="GF4" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="GF4" s="11" t="s">
+      <c r="GG4" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="GG4" s="11" t="s">
+      <c r="GH4" s="11" t="s">
         <v>414</v>
       </c>
-      <c r="GH4" s="11" t="s">
+      <c r="GI4" s="11" t="s">
         <v>415</v>
       </c>
-      <c r="GI4" s="11" t="s">
+      <c r="GJ4" s="11" t="s">
         <v>416</v>
       </c>
-      <c r="GJ4" s="11" t="s">
+      <c r="GK4" s="11" t="s">
         <v>417</v>
       </c>
-      <c r="GK4" s="11" t="s">
+      <c r="GL4" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="GL4" s="1" t="s">
+      <c r="GM4" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="GM4" s="1" t="s">
+      <c r="GN4" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="GN4" s="1" t="s">
+      <c r="GO4" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="GO4" s="1" t="s">
+      <c r="GP4" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="GP4" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="GQ4" s="1" t="s">
         <v>226</v>
       </c>
@@ -4601,10 +4598,10 @@
         <v>226</v>
       </c>
       <c r="GS4" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="GT4" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="GT4" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="GU4" s="1" t="s">
         <v>214</v>

--- a/ruoyi-modules/ruoyi-vehicle/src/main/resources/assets/COC导入模版.xlsx
+++ b/ruoyi-modules/ruoyi-vehicle/src/main/resources/assets/COC导入模版.xlsx
@@ -803,7 +803,7 @@
     <t>No</t>
   </si>
   <si>
-    <t>4,in-line</t>
+    <t>4,In line</t>
   </si>
   <si>
     <t>1598cm³</t>

--- a/ruoyi-modules/ruoyi-vehicle/src/main/resources/assets/COC导入模版.xlsx
+++ b/ruoyi-modules/ruoyi-vehicle/src/main/resources/assets/COC导入模版.xlsx
@@ -1133,11 +1133,14 @@
   </si>
   <si>
     <t>Chery Automobile Co., Ltd.(engine)
-Wuhu ACTECO Power Systems CO.,Ltd(EM1/EM2)
-heifei JEE Power Systems CO.,Ltd(Rear)</t>
-  </si>
-  <si>
-    <t>KPTZ220YMDA0</t>
+Wuhu ACTECO Power Systems CO.,Ltd.(EM1/EM2)
+heifei JEE Power Systems CO.,Ltd.(Rear)</t>
+  </si>
+  <si>
+    <t>Engine:SQRH4J15
+EM1&amp;EM2:KPTZ270YMXA0
+KPTZ180YMXA0
+Rear:TZ190XYCY1</t>
   </si>
   <si>
     <t>Positive ignition</t>
